--- a/data/horarios-141-2026-08-28.xlsx
+++ b/data/horarios-141-2026-08-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:12:37</t>
+          <t>Última actualización: 20:02:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 30</t>
+          <t>Total filas: 49</t>
         </is>
       </c>
     </row>
@@ -1263,6 +1263,500 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>16_P MOR-167 Y 521</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>83_ALUAR</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>17</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>27</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>32</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>33</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>46</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>49</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>55</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>72</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>79</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>80</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>89</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>92</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>95</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1275,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,14 +1782,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:12:37</t>
+          <t>Última actualización: 20:02:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -1408,6 +1902,58 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20:01:35</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>46</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1420,7 +1966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,14 +1979,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:12:37</t>
+          <t>Última actualización: 20:02:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -1579,6 +2125,110 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20:01:56</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20:01:56</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>66</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20:02:16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20:02:16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
